--- a/verification/cases/roundtrip/formulas_lookup/init.xlsx
+++ b/verification/cases/roundtrip/formulas_lookup/init.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/frl/Desktop/shortcut/stash/excel-test-sets/data/lookup-and-reference/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A58816FB-F2FB-3F45-8501-8028CC80CD18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{10A4E7C3-FD65-42DC-BB89-59CDACA1D446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="820" yWindow="960" windowWidth="28040" windowHeight="17180" xr2:uid="{C02FE269-2A1B-7842-BBB4-51E2A7D7A98E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{C02FE269-2A1B-7842-BBB4-51E2A7D7A98E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1339,7 +1339,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+  <wetp:taskpane dockstate="right" visibility="1" width="438" row="0">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -1362,24 +1362,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6140C96-6148-9541-AC66-05C431EDE65F}">
   <dimension ref="B2:K249"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="61.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.69921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="139" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.19921875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.19921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="19" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:11" ht="18" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -1391,7 +1391,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
@@ -1405,7 +1405,7 @@
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
         <v>4</v>
       </c>
@@ -1427,7 +1427,7 @@
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" s="7">
         <v>100</v>
       </c>
@@ -1449,7 +1449,7 @@
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B7" s="7">
         <v>200</v>
       </c>
@@ -1471,7 +1471,7 @@
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="7">
         <v>300</v>
       </c>
@@ -1493,7 +1493,7 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B9" s="7">
         <v>400</v>
       </c>
@@ -1515,7 +1515,7 @@
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B10" s="7">
         <v>500</v>
       </c>
@@ -1537,7 +1537,7 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B11" s="7">
         <v>600</v>
       </c>
@@ -1559,7 +1559,7 @@
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12" s="7">
         <v>700</v>
       </c>
@@ -1581,7 +1581,7 @@
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B13" s="7">
         <v>800</v>
       </c>
@@ -1603,7 +1603,7 @@
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -1615,7 +1615,7 @@
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>21</v>
       </c>
@@ -1629,7 +1629,7 @@
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B16" s="8" t="s">
         <v>22</v>
       </c>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="K16" s="2"/>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="5" t="s">
         <v>31</v>
       </c>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="K17" s="2"/>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="5" t="s">
         <v>32</v>
       </c>
@@ -1725,36 +1725,36 @@
       </c>
       <c r="K18" s="2"/>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="5" t="s">
         <v>33</v>
       </c>
       <c r="C19" s="9">
-        <f>C17-C18</f>
+        <f t="shared" ref="C19:I19" si="0">C17-C18</f>
         <v>400</v>
       </c>
       <c r="D19" s="9">
-        <f>D17-D18</f>
+        <f t="shared" si="0"/>
         <v>600</v>
       </c>
       <c r="E19" s="9">
-        <f>E17-E18</f>
+        <f t="shared" si="0"/>
         <v>800</v>
       </c>
       <c r="F19" s="9">
-        <f>F17-F18</f>
+        <f t="shared" si="0"/>
         <v>1000</v>
       </c>
       <c r="G19" s="9">
-        <f>G17-G18</f>
+        <f t="shared" si="0"/>
         <v>1000</v>
       </c>
       <c r="H19" s="9">
-        <f>H17-H18</f>
+        <f t="shared" si="0"/>
         <v>1800</v>
       </c>
       <c r="I19" s="9">
-        <f>I17-I18</f>
+        <f t="shared" si="0"/>
         <v>2800</v>
       </c>
       <c r="J19" s="9">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="K19" s="2"/>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -1774,7 +1774,7 @@
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
         <v>34</v>
       </c>
@@ -1788,7 +1788,7 @@
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B22" s="3" t="s">
         <v>35</v>
       </c>
@@ -1804,7 +1804,7 @@
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
         <v>36</v>
       </c>
@@ -1820,7 +1820,7 @@
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
         <v>37</v>
       </c>
@@ -1836,7 +1836,7 @@
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
         <v>38</v>
       </c>
@@ -1852,7 +1852,7 @@
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B26" s="3" t="s">
         <v>39</v>
       </c>
@@ -1868,7 +1868,7 @@
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B27" s="3" t="s">
         <v>40</v>
       </c>
@@ -1884,7 +1884,7 @@
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B28" s="3" t="s">
         <v>41</v>
       </c>
@@ -1900,7 +1900,7 @@
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B29" s="3" t="s">
         <v>42</v>
       </c>
@@ -1916,7 +1916,7 @@
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B30" s="3" t="s">
         <v>43</v>
       </c>
@@ -1932,7 +1932,7 @@
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
@@ -1944,7 +1944,7 @@
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
         <v>44</v>
       </c>
@@ -1958,7 +1958,7 @@
       <c r="J32" s="4"/>
       <c r="K32" s="4"/>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B33" s="11" t="s">
         <v>45</v>
       </c>
@@ -1982,7 +1982,7 @@
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B34" s="5">
         <v>300</v>
       </c>
@@ -2011,7 +2011,7 @@
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B35" s="5">
         <v>100</v>
       </c>
@@ -2040,7 +2040,7 @@
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B36" s="5">
         <v>800</v>
       </c>
@@ -2069,7 +2069,7 @@
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B37" s="5">
         <v>500</v>
       </c>
@@ -2098,7 +2098,7 @@
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
@@ -2110,7 +2110,7 @@
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
         <v>51</v>
       </c>
@@ -2124,7 +2124,7 @@
       <c r="J39" s="4"/>
       <c r="K39" s="4"/>
     </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B40" s="11" t="s">
         <v>45</v>
       </c>
@@ -2146,7 +2146,7 @@
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B41" s="5">
         <v>250</v>
       </c>
@@ -2172,7 +2172,7 @@
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B42" s="5">
         <v>350</v>
       </c>
@@ -2198,7 +2198,7 @@
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B43" s="5">
         <v>750</v>
       </c>
@@ -2224,7 +2224,7 @@
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
@@ -2236,7 +2236,7 @@
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B45" s="4" t="s">
         <v>54</v>
       </c>
@@ -2250,7 +2250,7 @@
       <c r="J45" s="4"/>
       <c r="K45" s="4"/>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B46" s="11" t="s">
         <v>55</v>
       </c>
@@ -2270,7 +2270,7 @@
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B47" s="5" t="s">
         <v>59</v>
       </c>
@@ -2292,7 +2292,7 @@
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B48" s="5" t="s">
         <v>61</v>
       </c>
@@ -2314,7 +2314,7 @@
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
     </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B49" s="5" t="s">
         <v>62</v>
       </c>
@@ -2336,7 +2336,7 @@
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
     </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B50" s="5" t="s">
         <v>63</v>
       </c>
@@ -2358,7 +2358,7 @@
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
     </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B51" s="5" t="s">
         <v>64</v>
       </c>
@@ -2380,7 +2380,7 @@
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
     </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B52" s="5" t="s">
         <v>65</v>
       </c>
@@ -2402,7 +2402,7 @@
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
     </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B53" s="5" t="s">
         <v>66</v>
       </c>
@@ -2424,7 +2424,7 @@
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
@@ -2436,7 +2436,7 @@
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
     </row>
-    <row r="55" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B55" s="4" t="s">
         <v>68</v>
       </c>
@@ -2450,7 +2450,7 @@
       <c r="J55" s="4"/>
       <c r="K55" s="4"/>
     </row>
-    <row r="56" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B56" s="11" t="s">
         <v>45</v>
       </c>
@@ -2474,7 +2474,7 @@
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
     </row>
-    <row r="57" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B57" s="5" t="s">
         <v>23</v>
       </c>
@@ -2503,7 +2503,7 @@
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
     </row>
-    <row r="58" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B58" s="5" t="s">
         <v>25</v>
       </c>
@@ -2532,7 +2532,7 @@
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
     </row>
-    <row r="59" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B59" s="5" t="s">
         <v>29</v>
       </c>
@@ -2561,7 +2561,7 @@
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
     </row>
-    <row r="60" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B60" s="5" t="s">
         <v>30</v>
       </c>
@@ -2590,7 +2590,7 @@
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
     </row>
-    <row r="61" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
@@ -2602,7 +2602,7 @@
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
     </row>
-    <row r="62" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B62" s="4" t="s">
         <v>73</v>
       </c>
@@ -2616,7 +2616,7 @@
       <c r="J62" s="4"/>
       <c r="K62" s="4"/>
     </row>
-    <row r="63" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B63" s="11" t="s">
         <v>55</v>
       </c>
@@ -2634,7 +2634,7 @@
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
     </row>
-    <row r="64" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B64" s="5" t="s">
         <v>76</v>
       </c>
@@ -2654,7 +2654,7 @@
       <c r="J64" s="2"/>
       <c r="K64" s="2"/>
     </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B65" s="5" t="s">
         <v>77</v>
       </c>
@@ -2674,7 +2674,7 @@
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
     </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B66" s="5" t="s">
         <v>64</v>
       </c>
@@ -2694,7 +2694,7 @@
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B67" s="5" t="s">
         <v>78</v>
       </c>
@@ -2714,7 +2714,7 @@
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
     </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
       <c r="D68" s="2"/>
@@ -2726,7 +2726,7 @@
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
     </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B69" s="4" t="s">
         <v>79</v>
       </c>
@@ -2740,7 +2740,7 @@
       <c r="J69" s="4"/>
       <c r="K69" s="4"/>
     </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B70" s="11" t="s">
         <v>45</v>
       </c>
@@ -2764,7 +2764,7 @@
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
     </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B71" s="5">
         <v>300</v>
       </c>
@@ -2793,7 +2793,7 @@
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
     </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B72" s="5">
         <v>100</v>
       </c>
@@ -2822,7 +2822,7 @@
       <c r="J72" s="2"/>
       <c r="K72" s="2"/>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B73" s="5">
         <v>800</v>
       </c>
@@ -2851,7 +2851,7 @@
       <c r="J73" s="2"/>
       <c r="K73" s="2"/>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B74" s="5">
         <v>500</v>
       </c>
@@ -2880,7 +2880,7 @@
       <c r="J74" s="2"/>
       <c r="K74" s="2"/>
     </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
       <c r="D75" s="2"/>
@@ -2892,7 +2892,7 @@
       <c r="J75" s="2"/>
       <c r="K75" s="2"/>
     </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B76" s="4" t="s">
         <v>85</v>
       </c>
@@ -2906,7 +2906,7 @@
       <c r="J76" s="4"/>
       <c r="K76" s="4"/>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B77" s="11" t="s">
         <v>45</v>
       </c>
@@ -2928,7 +2928,7 @@
       <c r="J77" s="2"/>
       <c r="K77" s="2"/>
     </row>
-    <row r="78" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B78" s="5">
         <v>250</v>
       </c>
@@ -2954,7 +2954,7 @@
       <c r="J78" s="2"/>
       <c r="K78" s="2"/>
     </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B79" s="5">
         <v>350</v>
       </c>
@@ -2980,7 +2980,7 @@
       <c r="J79" s="2"/>
       <c r="K79" s="2"/>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B80" s="5">
         <v>750</v>
       </c>
@@ -3006,7 +3006,7 @@
       <c r="J80" s="2"/>
       <c r="K80" s="2"/>
     </row>
-    <row r="81" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B81" s="5">
         <v>50</v>
       </c>
@@ -3032,7 +3032,7 @@
       <c r="J81" s="2"/>
       <c r="K81" s="2"/>
     </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
       <c r="D82" s="2"/>
@@ -3044,7 +3044,7 @@
       <c r="J82" s="2"/>
       <c r="K82" s="2"/>
     </row>
-    <row r="83" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B83" s="4" t="s">
         <v>90</v>
       </c>
@@ -3058,7 +3058,7 @@
       <c r="J83" s="4"/>
       <c r="K83" s="4"/>
     </row>
-    <row r="84" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B84" s="11" t="s">
         <v>45</v>
       </c>
@@ -3080,7 +3080,7 @@
       <c r="J84" s="2"/>
       <c r="K84" s="2"/>
     </row>
-    <row r="85" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B85" s="5">
         <v>300</v>
       </c>
@@ -3106,7 +3106,7 @@
       <c r="J85" s="2"/>
       <c r="K85" s="2"/>
     </row>
-    <row r="86" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B86" s="5">
         <v>500</v>
       </c>
@@ -3132,7 +3132,7 @@
       <c r="J86" s="2"/>
       <c r="K86" s="2"/>
     </row>
-    <row r="87" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B87" s="5" t="s">
         <v>12</v>
       </c>
@@ -3158,7 +3158,7 @@
       <c r="J87" s="2"/>
       <c r="K87" s="2"/>
     </row>
-    <row r="88" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
       <c r="D88" s="2"/>
@@ -3170,7 +3170,7 @@
       <c r="J88" s="2"/>
       <c r="K88" s="2"/>
     </row>
-    <row r="89" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B89" s="4" t="s">
         <v>95</v>
       </c>
@@ -3184,7 +3184,7 @@
       <c r="J89" s="4"/>
       <c r="K89" s="4"/>
     </row>
-    <row r="90" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B90" s="11" t="s">
         <v>45</v>
       </c>
@@ -3206,7 +3206,7 @@
       <c r="J90" s="2"/>
       <c r="K90" s="2"/>
     </row>
-    <row r="91" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B91" s="5">
         <v>300</v>
       </c>
@@ -3229,7 +3229,7 @@
       <c r="J91" s="2"/>
       <c r="K91" s="2"/>
     </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B92" s="5">
         <v>600</v>
       </c>
@@ -3252,7 +3252,7 @@
       <c r="J92" s="2"/>
       <c r="K92" s="2"/>
     </row>
-    <row r="93" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B93" s="5">
         <v>800</v>
       </c>
@@ -3275,7 +3275,7 @@
       <c r="J93" s="2"/>
       <c r="K93" s="2"/>
     </row>
-    <row r="94" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
       <c r="D94" s="2"/>
@@ -3287,7 +3287,7 @@
       <c r="J94" s="2"/>
       <c r="K94" s="2"/>
     </row>
-    <row r="95" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B95" s="4" t="s">
         <v>96</v>
       </c>
@@ -3301,7 +3301,7 @@
       <c r="J95" s="4"/>
       <c r="K95" s="4"/>
     </row>
-    <row r="96" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="96" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B96" s="11" t="s">
         <v>55</v>
       </c>
@@ -3323,7 +3323,7 @@
       <c r="J96" s="2"/>
       <c r="K96" s="2"/>
     </row>
-    <row r="97" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B97" s="5" t="s">
         <v>98</v>
       </c>
@@ -3347,7 +3347,7 @@
       <c r="J97" s="2"/>
       <c r="K97" s="2"/>
     </row>
-    <row r="98" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="98" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B98" s="5" t="s">
         <v>100</v>
       </c>
@@ -3371,7 +3371,7 @@
       <c r="J98" s="2"/>
       <c r="K98" s="2"/>
     </row>
-    <row r="99" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="99" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B99" s="5" t="s">
         <v>102</v>
       </c>
@@ -3395,7 +3395,7 @@
       <c r="J99" s="2"/>
       <c r="K99" s="2"/>
     </row>
-    <row r="100" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="100" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B100" s="5" t="s">
         <v>104</v>
       </c>
@@ -3419,7 +3419,7 @@
       <c r="J100" s="2"/>
       <c r="K100" s="2"/>
     </row>
-    <row r="101" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B101" s="5" t="s">
         <v>106</v>
       </c>
@@ -3443,7 +3443,7 @@
       <c r="J101" s="2"/>
       <c r="K101" s="2"/>
     </row>
-    <row r="102" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B102" s="5" t="s">
         <v>108</v>
       </c>
@@ -3467,7 +3467,7 @@
       <c r="J102" s="2"/>
       <c r="K102" s="2"/>
     </row>
-    <row r="103" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="103" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B103" s="5" t="s">
         <v>109</v>
       </c>
@@ -3491,7 +3491,7 @@
       <c r="J103" s="2"/>
       <c r="K103" s="2"/>
     </row>
-    <row r="104" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="104" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B104" s="5" t="s">
         <v>111</v>
       </c>
@@ -3515,7 +3515,7 @@
       <c r="J104" s="2"/>
       <c r="K104" s="2"/>
     </row>
-    <row r="105" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="105" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B105" s="5" t="s">
         <v>113</v>
       </c>
@@ -3539,7 +3539,7 @@
       <c r="J105" s="2"/>
       <c r="K105" s="2"/>
     </row>
-    <row r="106" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="106" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
       <c r="D106" s="2"/>
@@ -3551,7 +3551,7 @@
       <c r="J106" s="2"/>
       <c r="K106" s="2"/>
     </row>
-    <row r="107" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="107" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B107" s="4" t="s">
         <v>115</v>
       </c>
@@ -3565,7 +3565,7 @@
       <c r="J107" s="4"/>
       <c r="K107" s="4"/>
     </row>
-    <row r="108" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="108" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B108" s="11" t="s">
         <v>55</v>
       </c>
@@ -3585,7 +3585,7 @@
       <c r="J108" s="2"/>
       <c r="K108" s="2"/>
     </row>
-    <row r="109" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="109" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B109" s="5">
         <v>300</v>
       </c>
@@ -3608,7 +3608,7 @@
       <c r="J109" s="2"/>
       <c r="K109" s="2"/>
     </row>
-    <row r="110" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="110" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B110" s="5">
         <v>250</v>
       </c>
@@ -3631,7 +3631,7 @@
       <c r="J110" s="2"/>
       <c r="K110" s="2"/>
     </row>
-    <row r="111" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="111" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B111" s="5">
         <v>100</v>
       </c>
@@ -3654,7 +3654,7 @@
       <c r="J111" s="2"/>
       <c r="K111" s="2"/>
     </row>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="112" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B112" s="5">
         <v>800</v>
       </c>
@@ -3677,7 +3677,7 @@
       <c r="J112" s="2"/>
       <c r="K112" s="2"/>
     </row>
-    <row r="113" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="113" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B113" s="5">
         <v>50</v>
       </c>
@@ -3700,7 +3700,7 @@
       <c r="J113" s="2"/>
       <c r="K113" s="2"/>
     </row>
-    <row r="114" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="114" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B114" s="5">
         <v>999</v>
       </c>
@@ -3723,7 +3723,7 @@
       <c r="J114" s="2"/>
       <c r="K114" s="2"/>
     </row>
-    <row r="115" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B115" s="5" t="s">
         <v>9</v>
       </c>
@@ -3746,7 +3746,7 @@
       <c r="J115" s="2"/>
       <c r="K115" s="2"/>
     </row>
-    <row r="116" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="116" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B116" s="5" t="s">
         <v>16</v>
       </c>
@@ -3769,7 +3769,7 @@
       <c r="J116" s="2"/>
       <c r="K116" s="2"/>
     </row>
-    <row r="117" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
       <c r="D117" s="2"/>
@@ -3781,7 +3781,7 @@
       <c r="J117" s="2"/>
       <c r="K117" s="2"/>
     </row>
-    <row r="118" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="118" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B118" s="4" t="s">
         <v>118</v>
       </c>
@@ -3795,7 +3795,7 @@
       <c r="J118" s="4"/>
       <c r="K118" s="4"/>
     </row>
-    <row r="119" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="119" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B119" s="11" t="s">
         <v>55</v>
       </c>
@@ -3813,7 +3813,7 @@
       <c r="J119" s="2"/>
       <c r="K119" s="2"/>
     </row>
-    <row r="120" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="120" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B120" s="5" t="s">
         <v>119</v>
       </c>
@@ -3833,7 +3833,7 @@
       <c r="J120" s="2"/>
       <c r="K120" s="2"/>
     </row>
-    <row r="121" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="121" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B121" s="5" t="s">
         <v>120</v>
       </c>
@@ -3853,7 +3853,7 @@
       <c r="J121" s="2"/>
       <c r="K121" s="2"/>
     </row>
-    <row r="122" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="122" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B122" s="5" t="s">
         <v>121</v>
       </c>
@@ -3873,7 +3873,7 @@
       <c r="J122" s="2"/>
       <c r="K122" s="2"/>
     </row>
-    <row r="123" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="123" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B123" s="5" t="s">
         <v>122</v>
       </c>
@@ -3893,7 +3893,7 @@
       <c r="J123" s="2"/>
       <c r="K123" s="2"/>
     </row>
-    <row r="124" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="124" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B124" s="5" t="s">
         <v>123</v>
       </c>
@@ -3913,7 +3913,7 @@
       <c r="J124" s="2"/>
       <c r="K124" s="2"/>
     </row>
-    <row r="125" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="125" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B125" s="5" t="s">
         <v>124</v>
       </c>
@@ -3933,7 +3933,7 @@
       <c r="J125" s="2"/>
       <c r="K125" s="2"/>
     </row>
-    <row r="126" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="126" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B126" s="4"/>
       <c r="C126" s="4"/>
       <c r="D126" s="4"/>
@@ -3945,7 +3945,7 @@
       <c r="J126" s="4"/>
       <c r="K126" s="4"/>
     </row>
-    <row r="127" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="127" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B127" s="11" t="s">
         <v>125</v>
       </c>
@@ -3959,7 +3959,7 @@
       <c r="J127" s="2"/>
       <c r="K127" s="2"/>
     </row>
-    <row r="128" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="128" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B128" s="5" t="s">
         <v>45</v>
       </c>
@@ -3981,7 +3981,7 @@
       <c r="J128" s="2"/>
       <c r="K128" s="2"/>
     </row>
-    <row r="129" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="129" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B129" s="5">
         <v>300</v>
       </c>
@@ -4007,7 +4007,7 @@
       <c r="J129" s="2"/>
       <c r="K129" s="2"/>
     </row>
-    <row r="130" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="130" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B130" s="5">
         <v>250</v>
       </c>
@@ -4033,7 +4033,7 @@
       <c r="J130" s="2"/>
       <c r="K130" s="2"/>
     </row>
-    <row r="131" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="131" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B131" s="5">
         <v>50</v>
       </c>
@@ -4059,7 +4059,7 @@
       <c r="J131" s="2"/>
       <c r="K131" s="2"/>
     </row>
-    <row r="132" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="132" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B132" s="5">
         <v>999</v>
       </c>
@@ -4085,7 +4085,7 @@
       <c r="J132" s="2"/>
       <c r="K132" s="2"/>
     </row>
-    <row r="133" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="133" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B133" s="5" t="s">
         <v>11</v>
       </c>
@@ -4111,7 +4111,7 @@
       <c r="J133" s="2"/>
       <c r="K133" s="2"/>
     </row>
-    <row r="134" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="134" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
       <c r="D134" s="2"/>
@@ -4123,7 +4123,7 @@
       <c r="J134" s="2"/>
       <c r="K134" s="2"/>
     </row>
-    <row r="135" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="135" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B135" s="4" t="s">
         <v>126</v>
       </c>
@@ -4137,7 +4137,7 @@
       <c r="J135" s="4"/>
       <c r="K135" s="4"/>
     </row>
-    <row r="136" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="136" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B136" s="11" t="s">
         <v>45</v>
       </c>
@@ -4157,7 +4157,7 @@
       <c r="J136" s="2"/>
       <c r="K136" s="2"/>
     </row>
-    <row r="137" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="137" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B137" s="5">
         <v>300</v>
       </c>
@@ -4180,7 +4180,7 @@
       <c r="J137" s="2"/>
       <c r="K137" s="2"/>
     </row>
-    <row r="138" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="138" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B138" s="5" t="s">
         <v>12</v>
       </c>
@@ -4203,7 +4203,7 @@
       <c r="J138" s="2"/>
       <c r="K138" s="2"/>
     </row>
-    <row r="139" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="139" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B139" s="5" t="s">
         <v>10</v>
       </c>
@@ -4226,7 +4226,7 @@
       <c r="J139" s="2"/>
       <c r="K139" s="2"/>
     </row>
-    <row r="140" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="140" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
       <c r="D140" s="2"/>
@@ -4238,7 +4238,7 @@
       <c r="J140" s="2"/>
       <c r="K140" s="2"/>
     </row>
-    <row r="141" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="141" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B141" s="4" t="s">
         <v>127</v>
       </c>
@@ -4252,7 +4252,7 @@
       <c r="J141" s="4"/>
       <c r="K141" s="4"/>
     </row>
-    <row r="142" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="142" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B142" s="11" t="s">
         <v>55</v>
       </c>
@@ -4270,7 +4270,7 @@
       <c r="J142" s="2"/>
       <c r="K142" s="2"/>
     </row>
-    <row r="143" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="143" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B143" s="5" t="s">
         <v>128</v>
       </c>
@@ -4290,7 +4290,7 @@
       <c r="J143" s="2"/>
       <c r="K143" s="2"/>
     </row>
-    <row r="144" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="144" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B144" s="5" t="s">
         <v>129</v>
       </c>
@@ -4310,7 +4310,7 @@
       <c r="J144" s="2"/>
       <c r="K144" s="2"/>
     </row>
-    <row r="145" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="145" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B145" s="5" t="s">
         <v>130</v>
       </c>
@@ -4330,7 +4330,7 @@
       <c r="J145" s="2"/>
       <c r="K145" s="2"/>
     </row>
-    <row r="146" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="146" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B146" s="5" t="s">
         <v>131</v>
       </c>
@@ -4350,7 +4350,7 @@
       <c r="J146" s="2"/>
       <c r="K146" s="2"/>
     </row>
-    <row r="147" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="147" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B147" s="5" t="s">
         <v>132</v>
       </c>
@@ -4370,7 +4370,7 @@
       <c r="J147" s="2"/>
       <c r="K147" s="2"/>
     </row>
-    <row r="148" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="148" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B148" s="5" t="s">
         <v>133</v>
       </c>
@@ -4390,7 +4390,7 @@
       <c r="J148" s="2"/>
       <c r="K148" s="2"/>
     </row>
-    <row r="149" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="149" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B149" s="5" t="s">
         <v>134</v>
       </c>
@@ -4410,7 +4410,7 @@
       <c r="J149" s="2"/>
       <c r="K149" s="2"/>
     </row>
-    <row r="150" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="150" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B150" s="5" t="s">
         <v>135</v>
       </c>
@@ -4430,7 +4430,7 @@
       <c r="J150" s="2"/>
       <c r="K150" s="2"/>
     </row>
-    <row r="151" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="151" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B151" s="5" t="s">
         <v>136</v>
       </c>
@@ -4450,7 +4450,7 @@
       <c r="J151" s="2"/>
       <c r="K151" s="2"/>
     </row>
-    <row r="152" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="152" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
       <c r="D152" s="2"/>
@@ -4462,7 +4462,7 @@
       <c r="J152" s="2"/>
       <c r="K152" s="2"/>
     </row>
-    <row r="153" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="153" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B153" s="4" t="s">
         <v>137</v>
       </c>
@@ -4476,7 +4476,7 @@
       <c r="J153" s="4"/>
       <c r="K153" s="4"/>
     </row>
-    <row r="154" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="154" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B154" s="11" t="s">
         <v>55</v>
       </c>
@@ -4494,7 +4494,7 @@
       <c r="J154" s="2"/>
       <c r="K154" s="2"/>
     </row>
-    <row r="155" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="155" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B155" s="5" t="s">
         <v>138</v>
       </c>
@@ -4514,7 +4514,7 @@
       <c r="J155" s="2"/>
       <c r="K155" s="2"/>
     </row>
-    <row r="156" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="156" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B156" s="5" t="s">
         <v>139</v>
       </c>
@@ -4534,7 +4534,7 @@
       <c r="J156" s="2"/>
       <c r="K156" s="2"/>
     </row>
-    <row r="157" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="157" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B157" s="5" t="s">
         <v>140</v>
       </c>
@@ -4554,7 +4554,7 @@
       <c r="J157" s="2"/>
       <c r="K157" s="2"/>
     </row>
-    <row r="158" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="158" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B158" s="5" t="s">
         <v>141</v>
       </c>
@@ -4574,7 +4574,7 @@
       <c r="J158" s="2"/>
       <c r="K158" s="2"/>
     </row>
-    <row r="159" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="159" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B159" s="5" t="s">
         <v>142</v>
       </c>
@@ -4594,7 +4594,7 @@
       <c r="J159" s="2"/>
       <c r="K159" s="2"/>
     </row>
-    <row r="160" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="160" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B160" s="5" t="s">
         <v>143</v>
       </c>
@@ -4614,7 +4614,7 @@
       <c r="J160" s="2"/>
       <c r="K160" s="2"/>
     </row>
-    <row r="161" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="161" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B161" s="5" t="s">
         <v>144</v>
       </c>
@@ -4634,7 +4634,7 @@
       <c r="J161" s="2"/>
       <c r="K161" s="2"/>
     </row>
-    <row r="162" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="162" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B162" s="5" t="s">
         <v>145</v>
       </c>
@@ -4654,7 +4654,7 @@
       <c r="J162" s="2"/>
       <c r="K162" s="2"/>
     </row>
-    <row r="163" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="163" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B163" s="5" t="s">
         <v>146</v>
       </c>
@@ -4674,7 +4674,7 @@
       <c r="J163" s="2"/>
       <c r="K163" s="2"/>
     </row>
-    <row r="164" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="164" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B164" s="5" t="s">
         <v>147</v>
       </c>
@@ -4694,7 +4694,7 @@
       <c r="J164" s="2"/>
       <c r="K164" s="2"/>
     </row>
-    <row r="165" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="165" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
       <c r="D165" s="2"/>
@@ -4706,7 +4706,7 @@
       <c r="J165" s="2"/>
       <c r="K165" s="2"/>
     </row>
-    <row r="166" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="166" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B166" s="4" t="s">
         <v>148</v>
       </c>
@@ -4720,7 +4720,7 @@
       <c r="J166" s="4"/>
       <c r="K166" s="4"/>
     </row>
-    <row r="167" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="167" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B167" s="11" t="s">
         <v>55</v>
       </c>
@@ -4738,7 +4738,7 @@
       <c r="J167" s="2"/>
       <c r="K167" s="2"/>
     </row>
-    <row r="168" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="168" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B168" s="5" t="s">
         <v>149</v>
       </c>
@@ -4758,7 +4758,7 @@
       <c r="J168" s="2"/>
       <c r="K168" s="2"/>
     </row>
-    <row r="169" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="169" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B169" s="5" t="s">
         <v>150</v>
       </c>
@@ -4778,7 +4778,7 @@
       <c r="J169" s="2"/>
       <c r="K169" s="2"/>
     </row>
-    <row r="170" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="170" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B170" s="5" t="s">
         <v>151</v>
       </c>
@@ -4798,7 +4798,7 @@
       <c r="J170" s="2"/>
       <c r="K170" s="2"/>
     </row>
-    <row r="171" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="171" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B171" s="5" t="s">
         <v>152</v>
       </c>
@@ -4818,7 +4818,7 @@
       <c r="J171" s="2"/>
       <c r="K171" s="2"/>
     </row>
-    <row r="172" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="172" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B172" s="5" t="s">
         <v>153</v>
       </c>
@@ -4838,7 +4838,7 @@
       <c r="J172" s="2"/>
       <c r="K172" s="2"/>
     </row>
-    <row r="173" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="173" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B173" s="5" t="s">
         <v>154</v>
       </c>
@@ -4858,7 +4858,7 @@
       <c r="J173" s="2"/>
       <c r="K173" s="2"/>
     </row>
-    <row r="174" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="174" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B174" s="5" t="s">
         <v>155</v>
       </c>
@@ -4878,7 +4878,7 @@
       <c r="J174" s="2"/>
       <c r="K174" s="2"/>
     </row>
-    <row r="175" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="175" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B175" s="5" t="s">
         <v>156</v>
       </c>
@@ -4898,7 +4898,7 @@
       <c r="J175" s="2"/>
       <c r="K175" s="2"/>
     </row>
-    <row r="176" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="176" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B176" s="5" t="s">
         <v>157</v>
       </c>
@@ -4918,7 +4918,7 @@
       <c r="J176" s="2"/>
       <c r="K176" s="2"/>
     </row>
-    <row r="177" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="177" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B177" s="5" t="s">
         <v>158</v>
       </c>
@@ -4938,7 +4938,7 @@
       <c r="J177" s="2"/>
       <c r="K177" s="2"/>
     </row>
-    <row r="178" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="178" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B178" s="5" t="s">
         <v>159</v>
       </c>
@@ -4958,7 +4958,7 @@
       <c r="J178" s="2"/>
       <c r="K178" s="2"/>
     </row>
-    <row r="179" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="179" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
       <c r="D179" s="2"/>
@@ -4970,7 +4970,7 @@
       <c r="J179" s="2"/>
       <c r="K179" s="2"/>
     </row>
-    <row r="180" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="180" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B180" s="4" t="s">
         <v>160</v>
       </c>
@@ -4984,7 +4984,7 @@
       <c r="J180" s="4"/>
       <c r="K180" s="4"/>
     </row>
-    <row r="181" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="181" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B181" s="11" t="s">
         <v>55</v>
       </c>
@@ -5002,7 +5002,7 @@
       <c r="J181" s="2"/>
       <c r="K181" s="2"/>
     </row>
-    <row r="182" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="182" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B182" s="5" t="s">
         <v>161</v>
       </c>
@@ -5022,7 +5022,7 @@
       <c r="J182" s="2"/>
       <c r="K182" s="2"/>
     </row>
-    <row r="183" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="183" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B183" s="5" t="s">
         <v>162</v>
       </c>
@@ -5042,7 +5042,7 @@
       <c r="J183" s="2"/>
       <c r="K183" s="2"/>
     </row>
-    <row r="184" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="184" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B184" s="5" t="s">
         <v>163</v>
       </c>
@@ -5062,7 +5062,7 @@
       <c r="J184" s="2"/>
       <c r="K184" s="2"/>
     </row>
-    <row r="185" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="185" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B185" s="5" t="s">
         <v>164</v>
       </c>
@@ -5082,7 +5082,7 @@
       <c r="J185" s="2"/>
       <c r="K185" s="2"/>
     </row>
-    <row r="186" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="186" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B186" s="5" t="s">
         <v>165</v>
       </c>
@@ -5102,7 +5102,7 @@
       <c r="J186" s="2"/>
       <c r="K186" s="2"/>
     </row>
-    <row r="187" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="187" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B187" s="5" t="s">
         <v>166</v>
       </c>
@@ -5122,7 +5122,7 @@
       <c r="J187" s="2"/>
       <c r="K187" s="2"/>
     </row>
-    <row r="188" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="188" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B188" s="5" t="s">
         <v>167</v>
       </c>
@@ -5142,7 +5142,7 @@
       <c r="J188" s="2"/>
       <c r="K188" s="2"/>
     </row>
-    <row r="189" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="189" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
       <c r="D189" s="2"/>
@@ -5154,7 +5154,7 @@
       <c r="J189" s="2"/>
       <c r="K189" s="2"/>
     </row>
-    <row r="190" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="190" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B190" s="4" t="s">
         <v>168</v>
       </c>
@@ -5168,7 +5168,7 @@
       <c r="J190" s="4"/>
       <c r="K190" s="4"/>
     </row>
-    <row r="191" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="191" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B191" s="11" t="s">
         <v>55</v>
       </c>
@@ -5186,7 +5186,7 @@
       <c r="J191" s="2"/>
       <c r="K191" s="2"/>
     </row>
-    <row r="192" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="192" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B192" s="5" t="s">
         <v>161</v>
       </c>
@@ -5206,7 +5206,7 @@
       <c r="J192" s="2"/>
       <c r="K192" s="2"/>
     </row>
-    <row r="193" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="193" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B193" s="5" t="s">
         <v>162</v>
       </c>
@@ -5226,7 +5226,7 @@
       <c r="J193" s="2"/>
       <c r="K193" s="2"/>
     </row>
-    <row r="194" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="194" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B194" s="5" t="s">
         <v>169</v>
       </c>
@@ -5254,7 +5254,7 @@
       <c r="J194" s="2"/>
       <c r="K194" s="2"/>
     </row>
-    <row r="195" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="195" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B195" s="5" t="s">
         <v>170</v>
       </c>
@@ -5274,7 +5274,7 @@
       <c r="J195" s="2"/>
       <c r="K195" s="2"/>
     </row>
-    <row r="196" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="196" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B196" s="5" t="s">
         <v>166</v>
       </c>
@@ -5294,7 +5294,7 @@
       <c r="J196" s="2"/>
       <c r="K196" s="2"/>
     </row>
-    <row r="197" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="197" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B197" s="5" t="s">
         <v>171</v>
       </c>
@@ -5314,7 +5314,7 @@
       <c r="J197" s="2"/>
       <c r="K197" s="2"/>
     </row>
-    <row r="198" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="198" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B198" s="5" t="s">
         <v>146</v>
       </c>
@@ -5334,7 +5334,7 @@
       <c r="J198" s="2"/>
       <c r="K198" s="2"/>
     </row>
-    <row r="199" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="199" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
       <c r="D199" s="2"/>
@@ -5346,7 +5346,7 @@
       <c r="J199" s="2"/>
       <c r="K199" s="2"/>
     </row>
-    <row r="200" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="200" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B200" s="4" t="s">
         <v>172</v>
       </c>
@@ -5360,7 +5360,7 @@
       <c r="J200" s="4"/>
       <c r="K200" s="4"/>
     </row>
-    <row r="201" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="201" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B201" s="11" t="s">
         <v>55</v>
       </c>
@@ -5378,7 +5378,7 @@
       <c r="J201" s="2"/>
       <c r="K201" s="2"/>
     </row>
-    <row r="202" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="202" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B202" s="5" t="s">
         <v>173</v>
       </c>
@@ -5398,7 +5398,7 @@
       <c r="J202" s="2"/>
       <c r="K202" s="2"/>
     </row>
-    <row r="203" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="203" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B203" s="5" t="s">
         <v>174</v>
       </c>
@@ -5418,7 +5418,7 @@
       <c r="J203" s="2"/>
       <c r="K203" s="2"/>
     </row>
-    <row r="204" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="204" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B204" s="5" t="s">
         <v>113</v>
       </c>
@@ -5438,7 +5438,7 @@
       <c r="J204" s="2"/>
       <c r="K204" s="2"/>
     </row>
-    <row r="205" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="205" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B205" s="5" t="s">
         <v>111</v>
       </c>
@@ -5458,7 +5458,7 @@
       <c r="J205" s="2"/>
       <c r="K205" s="2"/>
     </row>
-    <row r="206" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="206" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B206" s="5" t="s">
         <v>175</v>
       </c>
@@ -5478,7 +5478,7 @@
       <c r="J206" s="2"/>
       <c r="K206" s="2"/>
     </row>
-    <row r="207" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="207" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B207" s="5" t="s">
         <v>176</v>
       </c>
@@ -5498,7 +5498,7 @@
       <c r="J207" s="2"/>
       <c r="K207" s="2"/>
     </row>
-    <row r="208" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="208" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B208" s="4" t="s">
         <v>177</v>
       </c>
@@ -5512,7 +5512,7 @@
       <c r="J208" s="4"/>
       <c r="K208" s="4"/>
     </row>
-    <row r="209" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="209" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B209" s="11" t="s">
         <v>55</v>
       </c>
@@ -5530,7 +5530,7 @@
       <c r="J209" s="2"/>
       <c r="K209" s="2"/>
     </row>
-    <row r="210" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="210" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B210" s="5" t="s">
         <v>173</v>
       </c>
@@ -5550,7 +5550,7 @@
       <c r="J210" s="2"/>
       <c r="K210" s="2"/>
     </row>
-    <row r="211" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="211" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B211" s="5" t="s">
         <v>174</v>
       </c>
@@ -5570,7 +5570,7 @@
       <c r="J211" s="2"/>
       <c r="K211" s="2"/>
     </row>
-    <row r="212" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="212" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B212" s="5" t="s">
         <v>113</v>
       </c>
@@ -5590,7 +5590,7 @@
       <c r="J212" s="2"/>
       <c r="K212" s="2"/>
     </row>
-    <row r="213" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="213" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B213" s="5" t="s">
         <v>111</v>
       </c>
@@ -5610,7 +5610,7 @@
       <c r="J213" s="2"/>
       <c r="K213" s="2"/>
     </row>
-    <row r="214" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="214" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B214" s="5" t="s">
         <v>175</v>
       </c>
@@ -5630,7 +5630,7 @@
       <c r="J214" s="2"/>
       <c r="K214" s="2"/>
     </row>
-    <row r="215" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="215" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B215" s="5" t="s">
         <v>176</v>
       </c>
@@ -5650,7 +5650,7 @@
       <c r="J215" s="2"/>
       <c r="K215" s="2"/>
     </row>
-    <row r="216" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="216" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B216" s="4" t="s">
         <v>178</v>
       </c>
@@ -5664,7 +5664,7 @@
       <c r="J216" s="4"/>
       <c r="K216" s="4"/>
     </row>
-    <row r="217" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="217" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B217" s="11" t="s">
         <v>55</v>
       </c>
@@ -5682,7 +5682,7 @@
       <c r="J217" s="2"/>
       <c r="K217" s="2"/>
     </row>
-    <row r="218" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="218" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B218" s="5" t="s">
         <v>179</v>
       </c>
@@ -5702,7 +5702,7 @@
       <c r="J218" s="2"/>
       <c r="K218" s="2"/>
     </row>
-    <row r="219" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="219" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B219" s="5" t="s">
         <v>180</v>
       </c>
@@ -5722,7 +5722,7 @@
       <c r="J219" s="2"/>
       <c r="K219" s="2"/>
     </row>
-    <row r="220" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="220" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B220" s="5" t="s">
         <v>181</v>
       </c>
@@ -5742,7 +5742,7 @@
       <c r="J220" s="2"/>
       <c r="K220" s="2"/>
     </row>
-    <row r="221" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="221" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B221" s="5" t="s">
         <v>182</v>
       </c>
@@ -5762,7 +5762,7 @@
       <c r="J221" s="2"/>
       <c r="K221" s="2"/>
     </row>
-    <row r="222" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="222" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B222" s="5" t="s">
         <v>140</v>
       </c>
@@ -5782,7 +5782,7 @@
       <c r="J222" s="2"/>
       <c r="K222" s="2"/>
     </row>
-    <row r="223" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="223" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B223" s="5" t="s">
         <v>183</v>
       </c>
@@ -5802,7 +5802,7 @@
       <c r="J223" s="2"/>
       <c r="K223" s="2"/>
     </row>
-    <row r="224" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="224" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B224" s="5" t="s">
         <v>184</v>
       </c>
@@ -5822,7 +5822,7 @@
       <c r="J224" s="2"/>
       <c r="K224" s="2"/>
     </row>
-    <row r="225" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="225" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B225" s="5" t="s">
         <v>185</v>
       </c>
@@ -5842,7 +5842,7 @@
       <c r="J225" s="2"/>
       <c r="K225" s="2"/>
     </row>
-    <row r="226" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="226" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B226" s="5" t="s">
         <v>186</v>
       </c>
@@ -5862,7 +5862,7 @@
       <c r="J226" s="2"/>
       <c r="K226" s="2"/>
     </row>
-    <row r="227" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="227" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B227" s="5" t="s">
         <v>187</v>
       </c>
@@ -5882,7 +5882,7 @@
       <c r="J227" s="2"/>
       <c r="K227" s="2"/>
     </row>
-    <row r="228" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="228" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B228" s="5" t="s">
         <v>188</v>
       </c>
@@ -5902,7 +5902,7 @@
       <c r="J228" s="2"/>
       <c r="K228" s="2"/>
     </row>
-    <row r="229" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="229" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B229" s="5" t="s">
         <v>189</v>
       </c>
@@ -5922,7 +5922,7 @@
       <c r="J229" s="2"/>
       <c r="K229" s="2"/>
     </row>
-    <row r="230" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="230" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B230" s="2"/>
       <c r="C230" s="2"/>
       <c r="D230" s="2"/>
@@ -5934,7 +5934,7 @@
       <c r="J230" s="2"/>
       <c r="K230" s="2"/>
     </row>
-    <row r="231" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="231" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B231" s="4" t="s">
         <v>190</v>
       </c>
@@ -5948,7 +5948,7 @@
       <c r="J231" s="4"/>
       <c r="K231" s="4"/>
     </row>
-    <row r="232" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="232" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B232" s="11" t="s">
         <v>55</v>
       </c>
@@ -5966,7 +5966,7 @@
       <c r="J232" s="2"/>
       <c r="K232" s="2"/>
     </row>
-    <row r="233" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="233" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B233" s="5" t="s">
         <v>173</v>
       </c>
@@ -5986,7 +5986,7 @@
       <c r="J233" s="2"/>
       <c r="K233" s="2"/>
     </row>
-    <row r="234" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="234" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B234" s="5" t="s">
         <v>191</v>
       </c>
@@ -6010,7 +6010,7 @@
       <c r="J234" s="2"/>
       <c r="K234" s="2"/>
     </row>
-    <row r="235" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="235" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B235" s="5" t="s">
         <v>192</v>
       </c>
@@ -6030,7 +6030,7 @@
       <c r="J235" s="2"/>
       <c r="K235" s="2"/>
     </row>
-    <row r="236" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="236" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B236" s="5" t="s">
         <v>193</v>
       </c>
@@ -6050,7 +6050,7 @@
       <c r="J236" s="2"/>
       <c r="K236" s="2"/>
     </row>
-    <row r="237" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="237" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B237" s="5" t="s">
         <v>194</v>
       </c>
@@ -6070,7 +6070,7 @@
       <c r="J237" s="2"/>
       <c r="K237" s="2"/>
     </row>
-    <row r="238" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="238" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B238" s="5" t="s">
         <v>195</v>
       </c>
@@ -6090,7 +6090,7 @@
       <c r="J238" s="2"/>
       <c r="K238" s="2"/>
     </row>
-    <row r="239" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="239" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B239" s="5" t="s">
         <v>196</v>
       </c>
@@ -6110,7 +6110,7 @@
       <c r="J239" s="2"/>
       <c r="K239" s="2"/>
     </row>
-    <row r="240" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="240" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B240" s="5" t="s">
         <v>197</v>
       </c>
@@ -6130,7 +6130,7 @@
       <c r="J240" s="2"/>
       <c r="K240" s="2"/>
     </row>
-    <row r="241" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="241" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B241" s="2"/>
       <c r="C241" s="2"/>
       <c r="D241" s="2"/>
@@ -6142,7 +6142,7 @@
       <c r="J241" s="2"/>
       <c r="K241" s="2"/>
     </row>
-    <row r="242" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="242" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B242" s="2"/>
       <c r="C242" s="2"/>
       <c r="D242" s="2"/>
@@ -6154,7 +6154,7 @@
       <c r="J242" s="2"/>
       <c r="K242" s="2"/>
     </row>
-    <row r="243" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="243" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B243" s="4" t="s">
         <v>0</v>
       </c>
@@ -6168,7 +6168,7 @@
       <c r="J243" s="4"/>
       <c r="K243" s="4"/>
     </row>
-    <row r="244" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="244" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B244" s="12" t="e">
         <v>#N/A</v>
       </c>
@@ -6184,7 +6184,7 @@
       <c r="J244" s="2"/>
       <c r="K244" s="2"/>
     </row>
-    <row r="245" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="245" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B245" s="12" t="e">
         <v>#REF!</v>
       </c>
@@ -6200,7 +6200,7 @@
       <c r="J245" s="2"/>
       <c r="K245" s="2"/>
     </row>
-    <row r="246" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="246" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B246" s="12" t="e">
         <v>#VALUE!</v>
       </c>
@@ -6216,7 +6216,7 @@
       <c r="J246" s="2"/>
       <c r="K246" s="2"/>
     </row>
-    <row r="247" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="247" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B247" s="12" t="s">
         <v>201</v>
       </c>
@@ -6232,7 +6232,7 @@
       <c r="J247" s="2"/>
       <c r="K247" s="2"/>
     </row>
-    <row r="248" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="248" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B248" s="12" t="s">
         <v>1</v>
       </c>
@@ -6248,7 +6248,7 @@
       <c r="J248" s="2"/>
       <c r="K248" s="2"/>
     </row>
-    <row r="249" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="249" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B249" s="12" t="s">
         <v>204</v>
       </c>
